--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.29876602231053</v>
+        <v>8.498549478625462</v>
       </c>
       <c r="D2" t="n">
-        <v>59.38599558192227</v>
+        <v>9.65022428206237</v>
       </c>
       <c r="E2" t="n">
-        <v>1.666186442239002</v>
+        <v>0.2707552968638378</v>
       </c>
       <c r="F2" t="n">
-        <v>5.208189725526822</v>
+        <v>0.8463308303981085</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.96639313783253</v>
+        <v>7.957038884897786</v>
       </c>
       <c r="D3" t="n">
-        <v>48.96961613086863</v>
+        <v>7.957562621266153</v>
       </c>
       <c r="E3" t="n">
-        <v>1.666186442239002</v>
+        <v>0.2707552968638378</v>
       </c>
       <c r="F3" t="n">
-        <v>5.208189725526822</v>
+        <v>0.8463308303981085</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
